--- a/public/fun/pack/xlsx/quote/견적서_33_행사·케이터링_완행열차창가.xlsx
+++ b/public/fun/pack/xlsx/quote/견적서_33_행사·케이터링_완행열차창가.xlsx
@@ -25,7 +25,7 @@
     <t>행사·케이터링 견적서</t>
   </si>
   <si>
-    <t>“느려도 반드시 도착하는 약속입니다”</t>
+    <t>“요청 사항을 반영해 수정할 수 있습니다”</t>
   </si>
   <si>
     <t>완행열차 창가 테마</t>
@@ -209,7 +209,7 @@
 • 결제: 행사 7일 전 50% / 행사 후 잔금</t>
   </si>
   <si>
-    <t>믿고 맡겨 주셔서 감사합니다.  ·  느려도 반드시 도착하는 약속입니다</t>
+    <t>믿고 맡겨 주셔서 감사합니다.  ·  요청 사항을 반영해 수정할 수 있습니다</t>
   </si>
 </sst>
 </file>

--- a/public/fun/pack/xlsx/quote/견적서_33_행사·케이터링_완행열차창가.xlsx
+++ b/public/fun/pack/xlsx/quote/견적서_33_행사·케이터링_완행열차창가.xlsx
@@ -20,12 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="62">
   <si>
     <t>행사·케이터링 견적서</t>
-  </si>
-  <si>
-    <t>“요청 사항을 반영해 수정할 수 있습니다”</t>
   </si>
   <si>
     <t>완행열차 창가 테마</t>
@@ -209,7 +206,7 @@
 • 결제: 행사 7일 전 50% / 행사 후 잔금</t>
   </si>
   <si>
-    <t>믿고 맡겨 주셔서 감사합니다.  ·  요청 사항을 반영해 수정할 수 있습니다</t>
+    <t>믿고 맡겨 주셔서 감사합니다.</t>
   </si>
 </sst>
 </file>
@@ -865,7 +862,7 @@
     <row r="1" spans="2:8" ht="14" customHeight="1"/>
     <row r="2" spans="2:8" ht="40" customHeight="1">
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -875,9 +872,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -887,12 +882,12 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -900,12 +895,12 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -913,7 +908,7 @@
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" s="5">
         <f>TODAY()</f>
@@ -921,7 +916,7 @@
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -929,7 +924,7 @@
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" s="6">
         <v>30</v>
@@ -939,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -947,14 +942,14 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -962,7 +957,7 @@
     </row>
     <row r="10" spans="2:8" ht="32" customHeight="1">
       <c r="B10" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="9">
@@ -976,25 +971,25 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="F12" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="G12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -1002,7 +997,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C13,'단가표'!$B$4:$B$33,0)),"")</f>
@@ -1029,7 +1024,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C14,'단가표'!$B$4:$B$33,0)),"")</f>
@@ -1056,7 +1051,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C15,'단가표'!$B$4:$B$33,0)),"")</f>
@@ -1083,7 +1078,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C16,'단가표'!$B$4:$B$33,0)),"")</f>
@@ -1360,7 +1355,7 @@
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -1374,7 +1369,7 @@
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -1387,7 +1382,7 @@
     </row>
     <row r="30" spans="2:8">
       <c r="B30" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
@@ -1401,13 +1396,13 @@
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G31" s="12"/>
       <c r="H31" s="16">
@@ -1417,7 +1412,7 @@
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -1431,10 +1426,10 @@
     </row>
     <row r="33" spans="2:8">
       <c r="B33" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="23" t="s">
         <v>60</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>61</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="23"/>
@@ -1468,7 +1463,7 @@
     </row>
     <row r="38" spans="2:8">
       <c r="B38" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" s="24"/>
       <c r="D38" s="24"/>
@@ -1537,7 +1532,7 @@
   <sheetData>
     <row r="1" spans="2:5">
       <c r="B1" s="25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
@@ -1545,27 +1540,27 @@
     </row>
     <row r="3" spans="2:5">
       <c r="B3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="21" t="s">
         <v>21</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>22</v>
       </c>
       <c r="E4" s="15">
         <v>212500</v>
@@ -1573,13 +1568,13 @@
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="21" t="s">
         <v>24</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>25</v>
       </c>
       <c r="E5" s="15">
         <v>102000</v>
@@ -1587,13 +1582,13 @@
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="21" t="s">
         <v>27</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>28</v>
       </c>
       <c r="E6" s="15">
         <v>10200</v>
@@ -1601,13 +1596,13 @@
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>27</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>28</v>
       </c>
       <c r="E7" s="15">
         <v>5100</v>
@@ -1615,13 +1610,13 @@
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="21" t="s">
         <v>31</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>32</v>
       </c>
       <c r="E8" s="15">
         <v>12800</v>
@@ -1629,13 +1624,13 @@
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="D9" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" s="15">
         <v>340000</v>
@@ -1643,13 +1638,13 @@
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="D10" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" s="15">
         <v>25500</v>
@@ -1657,13 +1652,13 @@
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>21</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>22</v>
       </c>
       <c r="E11" s="15">
         <v>425000</v>
@@ -1830,71 +1825,69 @@
       <c r="C2" s="26"/>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="27" t="s">
-        <v>1</v>
-      </c>
+      <c r="B3" s="27"/>
       <c r="C3" s="27"/>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="28"/>
     </row>
     <row r="5" spans="2:3" ht="6" customHeight="1"/>
     <row r="6" spans="2:3">
       <c r="B6" s="29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="30"/>
     </row>
     <row r="7" spans="2:3" ht="22" customHeight="1">
       <c r="B7" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="32" t="s">
         <v>4</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="32" customHeight="1">
       <c r="B8" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="32" t="s">
         <v>6</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="22" customHeight="1">
       <c r="B9" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="32" t="s">
         <v>8</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="32" customHeight="1">
       <c r="B10" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>10</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="28" customHeight="1">
       <c r="B12" s="33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="33"/>
     </row>
     <row r="13" spans="2:3" ht="28" customHeight="1">
       <c r="B13" s="33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="33"/>
     </row>
     <row r="15" spans="2:3">
       <c r="B15" s="34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="34"/>
     </row>

--- a/public/fun/pack/xlsx/quote/견적서_33_행사·케이터링_완행열차창가.xlsx
+++ b/public/fun/pack/xlsx/quote/견적서_33_행사·케이터링_완행열차창가.xlsx
@@ -962,7 +962,7 @@
       <c r="C10" s="8"/>
       <c r="D10" s="9">
         <f>H32</f>
-        <v>0</v>
+        <v>1028500</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
@@ -999,24 +999,24 @@
       <c r="C13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="12" t="str">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C13,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>일식</v>
       </c>
       <c r="E13" s="13">
         <v>2</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="14" t="str">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C13,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>식</v>
       </c>
       <c r="G13" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C13,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>212500</v>
       </c>
       <c r="H13" s="16">
         <f>IF(OR(E13="",G13=""),"",E13*G13)</f>
-        <v>0</v>
+        <v>425000</v>
       </c>
     </row>
     <row r="14" spans="2:8">
@@ -1026,24 +1026,24 @@
       <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="12" t="str">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C14,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>인당</v>
       </c>
       <c r="E14" s="13">
         <v>4</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="14" t="str">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C14,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>명</v>
       </c>
       <c r="G14" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C14,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>102000</v>
       </c>
       <c r="H14" s="16">
         <f>IF(OR(E14="",G14=""),"",E14*G14)</f>
-        <v>0</v>
+        <v>408000</v>
       </c>
     </row>
     <row r="15" spans="2:8">
@@ -1053,24 +1053,24 @@
       <c r="C15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="12" t="str">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C15,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>1인분</v>
       </c>
       <c r="E15" s="13">
         <v>6</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="14" t="str">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C15,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>개</v>
       </c>
       <c r="G15" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C15,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="H15" s="16">
         <f>IF(OR(E15="",G15=""),"",E15*G15)</f>
-        <v>0</v>
+        <v>61200</v>
       </c>
     </row>
     <row r="16" spans="2:8">
@@ -1080,24 +1080,24 @@
       <c r="C16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="12" t="str">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C16,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>1인분</v>
       </c>
       <c r="E16" s="13">
         <v>8</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="14" t="str">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C16,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>개</v>
       </c>
       <c r="G16" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C16,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="H16" s="16">
         <f>IF(OR(E16="",G16=""),"",E16*G16)</f>
-        <v>0</v>
+        <v>40800</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -1107,20 +1107,20 @@
       <c r="C17" s="4"/>
       <c r="D17" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C17,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E17" s="13"/>
       <c r="F17" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C17,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G17" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C17,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H17" s="16">
         <f>IF(OR(E17="",G17=""),"",E17*G17)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -1130,20 +1130,20 @@
       <c r="C18" s="4"/>
       <c r="D18" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C18,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C18,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G18" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C18,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H18" s="16">
         <f>IF(OR(E18="",G18=""),"",E18*G18)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="19" spans="2:8">
@@ -1153,20 +1153,20 @@
       <c r="C19" s="4"/>
       <c r="D19" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C19,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C19,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G19" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C19,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H19" s="16">
         <f>IF(OR(E19="",G19=""),"",E19*G19)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="2:8">
@@ -1176,20 +1176,20 @@
       <c r="C20" s="4"/>
       <c r="D20" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C20,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C20,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G20" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C20,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H20" s="16">
         <f>IF(OR(E20="",G20=""),"",E20*G20)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="2:8">
@@ -1199,20 +1199,20 @@
       <c r="C21" s="4"/>
       <c r="D21" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C21,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C21,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G21" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C21,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H21" s="16">
         <f>IF(OR(E21="",G21=""),"",E21*G21)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="2:8">
@@ -1222,20 +1222,20 @@
       <c r="C22" s="4"/>
       <c r="D22" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C22,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C22,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G22" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C22,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H22" s="16">
         <f>IF(OR(E22="",G22=""),"",E22*G22)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="23" spans="2:8">
@@ -1245,20 +1245,20 @@
       <c r="C23" s="4"/>
       <c r="D23" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C23,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C23,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G23" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C23,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H23" s="16">
         <f>IF(OR(E23="",G23=""),"",E23*G23)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="24" spans="2:8">
@@ -1268,20 +1268,20 @@
       <c r="C24" s="4"/>
       <c r="D24" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C24,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C24,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G24" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C24,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H24" s="16">
         <f>IF(OR(E24="",G24=""),"",E24*G24)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="25" spans="2:8">
@@ -1291,20 +1291,20 @@
       <c r="C25" s="4"/>
       <c r="D25" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C25,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E25" s="13"/>
       <c r="F25" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C25,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G25" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C25,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H25" s="16">
         <f>IF(OR(E25="",G25=""),"",E25*G25)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="26" spans="2:8">
@@ -1314,20 +1314,20 @@
       <c r="C26" s="4"/>
       <c r="D26" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C26,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C26,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G26" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C26,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H26" s="16">
         <f>IF(OR(E26="",G26=""),"",E26*G26)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="27" spans="2:8">
@@ -1337,20 +1337,20 @@
       <c r="C27" s="4"/>
       <c r="D27" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C27,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C27,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G27" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C27,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H27" s="16">
         <f>IF(OR(E27="",G27=""),"",E27*G27)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="28" spans="2:8">
@@ -1364,7 +1364,7 @@
       <c r="G28" s="17"/>
       <c r="H28" s="18">
         <f>SUM(H13:H27)</f>
-        <v>0</v>
+        <v>935000</v>
       </c>
     </row>
     <row r="29" spans="2:8">
@@ -1391,7 +1391,7 @@
       <c r="G30" s="19"/>
       <c r="H30" s="20">
         <f>H28-H29</f>
-        <v>0</v>
+        <v>935000</v>
       </c>
     </row>
     <row r="31" spans="2:8">
@@ -1407,7 +1407,7 @@
       <c r="G31" s="12"/>
       <c r="H31" s="16">
         <f>IF(F31="별도",ROUND(H30*0.1,0),IF(F31="포함",ROUND(H30/11,0),0))</f>
-        <v>0</v>
+        <v>93500</v>
       </c>
     </row>
     <row r="32" spans="2:8">
@@ -1421,7 +1421,7 @@
       <c r="G32" s="17"/>
       <c r="H32" s="22">
         <f>H30+IF(F31="별도",H31,0)</f>
-        <v>0</v>
+        <v>1028500</v>
       </c>
     </row>
     <row r="33" spans="2:8">

--- a/public/fun/pack/xlsx/quote/견적서_33_행사·케이터링_완행열차창가.xlsx
+++ b/public/fun/pack/xlsx/quote/견적서_33_행사·케이터링_완행열차창가.xlsx
@@ -61,7 +61,7 @@
     <t>사업자등록번호·연락처는 ‘견적서’에 직접 입력하세요.</t>
   </si>
   <si>
-    <t>우체국보험 상담 안내 · 자유롭게 고쳐 쓰세요</t>
+    <t>반딧불이의 곳간 · 자유롭게 고쳐 쓰세요</t>
   </si>
   <si>
     <t>단가표 — 자주 쓰는 품목을 적어 두세요</t>
@@ -214,9 +214,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="m&quot;월&quot; d&quot;일&quot;"/>
     <numFmt numFmtId="165" formatCode="0&quot;일&quot;"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd&quot;까지&quot;"/>
+    <numFmt numFmtId="166" formatCode="m&quot;월&quot; d&quot;일 까지&quot;"/>
     <numFmt numFmtId="167" formatCode="&quot;₩ &quot;#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0"/>
   </numFmts>
